--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/FLORIDA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/FLORIDA_2019.xlsx
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C164">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C213">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C359">
@@ -7843,7 +7843,7 @@
         <v>251</v>
       </c>
       <c r="D416">
-        <v>0.009013214593507613</v>
+        <v>0.009013214593507611</v>
       </c>
     </row>
     <row r="417">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C884">
@@ -17232,7 +17232,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C938">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C939">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C999">
